--- a/Tests/g17_setup1_with_3ed_sim_outputs.xlsx
+++ b/Tests/g17_setup1_with_3ed_sim_outputs.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5440292_ad_unsw_edu_au/Documents/MyPhD-Workspace/Codes/LoRaMeshSimulator-V3/Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_F44E90179F54AE5EED5B449649FCEE3F2E39860D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C9EF487-47B3-41FE-BF45-F3EBD2C27317}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_F44EEB0FD870365EED5B449649C126FA3AABF9F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590C7A47-414F-4832-98FB-7C6B2951DFCE}"/>
   <bookViews>
-    <workbookView xWindow="29988" yWindow="756" windowWidth="17400" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
   <si>
     <t>---&gt; DER:</t>
   </si>
@@ -32,6 +45,18 @@
   </si>
   <si>
     <t>---&gt; Max Latency:</t>
+  </si>
+  <si>
+    <t>Avg. interval of an ED transmitting DATA (s)</t>
+  </si>
+  <si>
+    <t>Packet Delivery Ratio (PDR)</t>
+  </si>
+  <si>
+    <t>Deployment- Packets Received</t>
+  </si>
+  <si>
+    <t>PDR</t>
   </si>
 </sst>
 </file>
@@ -84,6 +109,1112 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14405503293412891"/>
+          <c:y val="0.1133048968317701"/>
+          <c:w val="0.82293522529325969"/>
+          <c:h val="0.72290926719404414"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Simulation</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$O$2:$O$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$2:$G$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.93100000000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96699999999999997</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.99299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B705-45EB-B6A5-582019340B25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Real Deployment</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$U$2:$U$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.91100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94799999999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.95499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.98599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.99099999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B705-45EB-B6A5-582019340B25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1913827839"/>
+        <c:axId val="1913825439"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1913827839"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Avg. interval of an ED transmitting DATA (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.23689304132426295"/>
+              <c:y val="0.91590294396740479"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913825439"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1913825439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0.84000000000000008"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Packet Delivery Ratio (PDR)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.1427633327207419E-2"/>
+              <c:y val="0.21860390921269895"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1913827839"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>40444</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>109905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>103161</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>175846</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD3F3CF2-99A9-9325-6DDF-5C2921C1A4EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -371,7 +1502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.44140625" customWidth="1"/>
@@ -381,50 +1512,26 @@
     <col min="10" max="10" width="16.44140625" customWidth="1"/>
     <col min="11" max="11" width="14.21875" customWidth="1"/>
     <col min="12" max="12" width="13.109375" customWidth="1"/>
+    <col min="18" max="18" width="2" customWidth="1"/>
+    <col min="19" max="19" width="3.44140625" customWidth="1"/>
+    <col min="20" max="20" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="C1">
-        <v>3</v>
-      </c>
-      <c r="D1">
-        <v>10000</v>
-      </c>
-      <c r="E1">
-        <v>1000</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1">
-        <v>0.89100000000000001</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1">
-        <v>6214.8562144736006</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1">
-        <v>44.326609136769548</v>
-      </c>
-      <c r="L1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1">
-        <v>40393.759652144741</v>
+      <c r="O1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -435,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E2">
         <v>1000</v>
@@ -444,28 +1551,39 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.91200000000000003</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>4963.6605942138194</v>
+        <v>10314.840532610369</v>
       </c>
       <c r="J2" t="s">
         <v>2</v>
       </c>
       <c r="K2">
-        <v>39.535311982966959</v>
+        <v>620.42376233544201</v>
       </c>
       <c r="L2" t="s">
         <v>3</v>
       </c>
       <c r="M2">
-        <v>50331.18309834972</v>
+        <v>35238.868000862421</v>
+      </c>
+      <c r="O2">
+        <f>D2/1000</f>
+        <v>10</v>
+      </c>
+      <c r="T2">
+        <v>911</v>
+      </c>
+      <c r="U2">
+        <f>T2/1000</f>
+        <v>0.91100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -476,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E3">
         <v>1000</v>
@@ -485,28 +1603,39 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0.92900000000000005</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4546.0394857861074</v>
+        <v>6881.4543421953558</v>
       </c>
       <c r="J3" t="s">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>36.22827111184597</v>
+        <v>418.52950336271903</v>
       </c>
       <c r="L3" t="s">
         <v>3</v>
       </c>
       <c r="M3">
-        <v>28589.188517164439</v>
+        <v>23268.401874998352</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O7" si="0">D3/1000</f>
+        <v>20</v>
+      </c>
+      <c r="T3">
+        <v>948</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U7" si="1">T3/1000</f>
+        <v>0.94799999999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -517,7 +1646,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E4">
         <v>1000</v>
@@ -526,28 +1655,39 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0.94599999999999995</v>
+        <v>0.97</v>
       </c>
       <c r="H4" t="s">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>4161.4605554375576</v>
+        <v>5780.0526471245321</v>
       </c>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4">
-        <v>36.773378594079993</v>
+        <v>402.87907738785731</v>
       </c>
       <c r="L4" t="s">
         <v>3</v>
       </c>
       <c r="M4">
-        <v>29571.187566513199</v>
+        <v>21732.349125525448</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="T4">
+        <v>955</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="1"/>
+        <v>0.95499999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -558,7 +1698,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="E5">
         <v>1000</v>
@@ -567,28 +1707,39 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0.94899999999999995</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>4088.0721424540611</v>
+        <v>5792.9292153384376</v>
       </c>
       <c r="J5" t="s">
         <v>2</v>
       </c>
       <c r="K5">
-        <v>33.578984665684402</v>
+        <v>862.83593815658242</v>
       </c>
       <c r="L5" t="s">
         <v>3</v>
       </c>
       <c r="M5">
-        <v>20720.074479687959</v>
+        <v>21185.416493543369</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="T5">
+        <v>965</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="1"/>
+        <v>0.96499999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -599,7 +1750,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="E6">
         <v>1000</v>
@@ -608,28 +1759,92 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.96799999999999997</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>3636.1149560764361</v>
+        <v>6105.0548064783197</v>
       </c>
       <c r="J6" t="s">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>38.222822342067957</v>
+        <v>915.67072846589144</v>
       </c>
       <c r="L6" t="s">
         <v>3</v>
       </c>
       <c r="M6">
-        <v>21565.191792225469</v>
+        <v>30750.040371114621</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="T6">
+        <v>986</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="1"/>
+        <v>0.98599999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>60000</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0.995</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>4468.9598326136129</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <v>483.45873185992241</v>
+      </c>
+      <c r="L7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>24689.458720670082</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="T7">
+        <v>991</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="1"/>
+        <v>0.99099999999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>